--- a/img/署名表格.xlsx
+++ b/img/署名表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\yys\img\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D237F8-D3CA-47EA-8A5C-D1FFD1A026C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E460A-2B02-4786-A4D0-7746FA1ADC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3928,7 +3928,7 @@
         <v>325</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1</v>
+        <v>155</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">

--- a/img/署名表格.xlsx
+++ b/img/署名表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\yys\img\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E460A-2B02-4786-A4D0-7746FA1ADC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1993FD-C13C-4BA3-AC4C-C1020FB21864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3496,7 +3496,7 @@
         <v>270</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
@@ -3504,7 +3504,7 @@
         <v>271</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
